--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.19323022375525</v>
+        <v>12.86889991136023</v>
       </c>
       <c r="D2" t="n">
-        <v>74.29107190894197</v>
+        <v>12.07229918520307</v>
       </c>
       <c r="E2" t="n">
-        <v>23.94662362579333</v>
+        <v>3.891326339191416</v>
       </c>
       <c r="F2" t="n">
-        <v>13.55825211865706</v>
+        <v>2.203215969281773</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.181136597980082</v>
+        <v>1.491934697171763</v>
       </c>
       <c r="D3" t="n">
-        <v>68.53349049668508</v>
+        <v>11.13669220571133</v>
       </c>
       <c r="E3" t="n">
-        <v>23.94662362579333</v>
+        <v>3.891326339191416</v>
       </c>
       <c r="F3" t="n">
-        <v>13.55825211865706</v>
+        <v>2.203215969281773</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.65883765906234</v>
+        <v>8.394561119597629</v>
       </c>
       <c r="D4" t="n">
-        <v>40.54073384420655</v>
+        <v>6.587869249683565</v>
       </c>
       <c r="E4" t="n">
-        <v>23.94662362579333</v>
+        <v>3.891326339191416</v>
       </c>
       <c r="F4" t="n">
-        <v>13.55825211865706</v>
+        <v>2.203215969281773</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>63.23047215724448</v>
+        <v>10.27495172555223</v>
       </c>
       <c r="D5" t="n">
-        <v>77.11886783960745</v>
+        <v>12.53181602393621</v>
       </c>
       <c r="E5" t="n">
-        <v>23.94662362579333</v>
+        <v>3.891326339191416</v>
       </c>
       <c r="F5" t="n">
-        <v>13.55825211865706</v>
+        <v>2.203215969281773</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.54876407587675</v>
+        <v>10.65167416232997</v>
       </c>
       <c r="D6" t="n">
-        <v>74.82009866863515</v>
+        <v>12.15826603365321</v>
       </c>
       <c r="E6" t="n">
-        <v>23.94662362579333</v>
+        <v>3.891326339191416</v>
       </c>
       <c r="F6" t="n">
-        <v>13.55825211865706</v>
+        <v>2.203215969281773</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
